--- a/public/templates/06_전화주문_택배송장_관리/전화주문_입금확인_택배송장_관리.xlsx
+++ b/public/templates/06_전화주문_택배송장_관리/전화주문_입금확인_택배송장_관리.xlsx
@@ -1332,12 +1332,34 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="A4" s="7" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>이고객</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>010-0000-0002</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>부산시 ○○구 ○○로 20</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>202동 303호</t>
+        </is>
+      </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6615,229 +6637,291 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="str">
         <f aca="false">IF($C3="","",TEXT($B3,"yymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$3:$B3,$B3),"000"))</f>
-        <v/>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="7"/>
+        <v>260903-001</v>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1001</v>
+      </c>
       <c r="D3" s="12" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(고객명부!$B$3:$B$502,MATCH($C3,고객명부!$A$3:$A$502,0)),"미등록고객"))</f>
-        <v/>
+        <v>김고객</v>
       </c>
       <c r="E3" s="12" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(고객명부!$C$3:$C$502,MATCH($C3,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>010-0000-0000</v>
       </c>
       <c r="F3" s="12" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(고객명부!$D$3:$D$502,MATCH($C3,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>12345</v>
       </c>
       <c r="G3" s="12" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX(고객명부!$E$3:$E$502,MATCH($C3,고객명부!$A$3:$A$502,0))&amp;" "&amp;INDEX(고객명부!$F$3:$F$502,MATCH($C3,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H3" s="7"/>
+        <v>서울시 ○○구 ○○로 10 101동 101호</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>사과 부사 5kg</t>
+        </is>
+      </c>
       <c r="I3" s="12" t="str">
         <f aca="false">IF($H3="","",IFERROR(INDEX(상품목록!$B$3:$B$102,MATCH($H3,상품목록!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="J3" s="14" t="str">
+        <v>5kg (특)</v>
+      </c>
+      <c r="J3" s="14" t="n">
         <f aca="false">IF($H3="","",IFERROR(INDEX(상품목록!$C$3:$C$102,MATCH($H3,상품목록!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="14" t="str">
+        <v>35000</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="14" t="n">
         <f aca="false">IF(OR($J3="",$K3=""),"",ROUND($J3*$K3,0))</f>
-        <v/>
-      </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="14" t="str">
+        <v>70000</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N3" s="14" t="n">
         <f aca="false">IF($L3="","",$L3+IF($M3="",0,$M3))</f>
-        <v/>
-      </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="7"/>
+        <v>73500</v>
+      </c>
+      <c r="O3" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
       <c r="Q3" s="12" t="str">
         <f aca="false">IF($C3="","",IF($P3&lt;&gt;"","발송완료",IF($O3&lt;&gt;"","입금완료","입금대기")))</f>
-        <v/>
-      </c>
-      <c r="R3" s="12" t="str">
+        <v>발송완료</v>
+      </c>
+      <c r="R3" s="12" t="n">
         <f aca="false">IF($C3="","",COUNTIFS($C$3:$C3,$C3))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S3" s="12" t="str">
         <f aca="false">IF($C3="","",$C3&amp;"|"&amp;$R3)</f>
-        <v/>
+        <v>1001|1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="str">
         <f aca="false">IF($C4="","",TEXT($B4,"yymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$3:$B4,$B4),"000"))</f>
-        <v/>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="7"/>
+        <v>260903-002</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1002</v>
+      </c>
       <c r="D4" s="12" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(고객명부!$B$3:$B$502,MATCH($C4,고객명부!$A$3:$A$502,0)),"미등록고객"))</f>
-        <v/>
+        <v>이고객</v>
       </c>
       <c r="E4" s="12" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(고객명부!$C$3:$C$502,MATCH($C4,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>010-0000-0002</v>
       </c>
       <c r="F4" s="12" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(고객명부!$D$3:$D$502,MATCH($C4,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>54321</v>
       </c>
       <c r="G4" s="12" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX(고객명부!$E$3:$E$502,MATCH($C4,고객명부!$A$3:$A$502,0))&amp;" "&amp;INDEX(고객명부!$F$3:$F$502,MATCH($C4,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H4" s="7"/>
+        <v>부산시 ○○구 ○○로 20 202동 303호</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>배 신고 7.5kg</t>
+        </is>
+      </c>
       <c r="I4" s="12" t="str">
         <f aca="false">IF($H4="","",IFERROR(INDEX(상품목록!$B$3:$B$102,MATCH($H4,상품목록!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="J4" s="14" t="str">
+        <v>7.5kg</v>
+      </c>
+      <c r="J4" s="14" t="n">
         <f aca="false">IF($H4="","",IFERROR(INDEX(상품목록!$C$3:$C$102,MATCH($H4,상품목록!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="14" t="str">
+        <v>48000</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="14" t="n">
         <f aca="false">IF(OR($J4="",$K4=""),"",ROUND($J4*$K4,0))</f>
-        <v/>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="14" t="str">
+        <v>48000</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N4" s="14" t="n">
         <f aca="false">IF($L4="","",$L4+IF($M4="",0,$M4))</f>
-        <v/>
-      </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="7"/>
+        <v>51500</v>
+      </c>
+      <c r="O4" s="13" t="n">
+        <v>46269</v>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>1234567891</t>
+        </is>
+      </c>
       <c r="Q4" s="12" t="str">
         <f aca="false">IF($C4="","",IF($P4&lt;&gt;"","발송완료",IF($O4&lt;&gt;"","입금완료","입금대기")))</f>
-        <v/>
-      </c>
-      <c r="R4" s="12" t="str">
+        <v>발송완료</v>
+      </c>
+      <c r="R4" s="12" t="n">
         <f aca="false">IF($C4="","",COUNTIFS($C$3:$C4,$C4))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S4" s="12" t="str">
         <f aca="false">IF($C4="","",$C4&amp;"|"&amp;$R4)</f>
-        <v/>
+        <v>1002|1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="str">
         <f aca="false">IF($C5="","",TEXT($B5,"yymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$3:$B5,$B5),"000"))</f>
-        <v/>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="7"/>
+        <v>260909-001</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>1001</v>
+      </c>
       <c r="D5" s="12" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(고객명부!$B$3:$B$502,MATCH($C5,고객명부!$A$3:$A$502,0)),"미등록고객"))</f>
-        <v/>
+        <v>김고객</v>
       </c>
       <c r="E5" s="12" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(고객명부!$C$3:$C$502,MATCH($C5,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>010-0000-0000</v>
       </c>
       <c r="F5" s="12" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(고객명부!$D$3:$D$502,MATCH($C5,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>12345</v>
       </c>
       <c r="G5" s="12" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX(고객명부!$E$3:$E$502,MATCH($C5,고객명부!$A$3:$A$502,0))&amp;" "&amp;INDEX(고객명부!$F$3:$F$502,MATCH($C5,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H5" s="7"/>
+        <v>서울시 ○○구 ○○로 10 101동 101호</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>사과 부사 10kg</t>
+        </is>
+      </c>
       <c r="I5" s="12" t="str">
         <f aca="false">IF($H5="","",IFERROR(INDEX(상품목록!$B$3:$B$102,MATCH($H5,상품목록!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="J5" s="14" t="str">
+        <v>10kg (상)</v>
+      </c>
+      <c r="J5" s="14" t="n">
         <f aca="false">IF($H5="","",IFERROR(INDEX(상품목록!$C$3:$C$102,MATCH($H5,상품목록!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="14" t="str">
+        <v>55000</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="14" t="n">
         <f aca="false">IF(OR($J5="",$K5=""),"",ROUND($J5*$K5,0))</f>
-        <v/>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="14" t="str">
+        <v>55000</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N5" s="14" t="n">
         <f aca="false">IF($L5="","",$L5+IF($M5="",0,$M5))</f>
-        <v/>
-      </c>
-      <c r="O5" s="13"/>
+        <v>58500</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>46274</v>
+      </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="12" t="str">
         <f aca="false">IF($C5="","",IF($P5&lt;&gt;"","발송완료",IF($O5&lt;&gt;"","입금완료","입금대기")))</f>
-        <v/>
-      </c>
-      <c r="R5" s="12" t="str">
+        <v>입금완료</v>
+      </c>
+      <c r="R5" s="12" t="n">
         <f aca="false">IF($C5="","",COUNTIFS($C$3:$C5,$C5))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S5" s="12" t="str">
         <f aca="false">IF($C5="","",$C5&amp;"|"&amp;$R5)</f>
-        <v/>
+        <v>1001|2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="str">
         <f aca="false">IF($C6="","",TEXT($B6,"yymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$3:$B6,$B6),"000"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7"/>
+        <v>260912-001</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1002</v>
+      </c>
       <c r="D6" s="12" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(고객명부!$B$3:$B$502,MATCH($C6,고객명부!$A$3:$A$502,0)),"미등록고객"))</f>
-        <v/>
+        <v>이고객</v>
       </c>
       <c r="E6" s="12" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(고객명부!$C$3:$C$502,MATCH($C6,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>010-0000-0002</v>
       </c>
       <c r="F6" s="12" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(고객명부!$D$3:$D$502,MATCH($C6,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
+        <v>54321</v>
       </c>
       <c r="G6" s="12" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX(고객명부!$E$3:$E$502,MATCH($C6,고객명부!$A$3:$A$502,0))&amp;" "&amp;INDEX(고객명부!$F$3:$F$502,MATCH($C6,고객명부!$A$3:$A$502,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H6" s="7"/>
+        <v>부산시 ○○구 ○○로 20 202동 303호</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>사과 부사 5kg</t>
+        </is>
+      </c>
       <c r="I6" s="12" t="str">
         <f aca="false">IF($H6="","",IFERROR(INDEX(상품목록!$B$3:$B$102,MATCH($H6,상품목록!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="J6" s="14" t="str">
+        <v>5kg (특)</v>
+      </c>
+      <c r="J6" s="14" t="n">
         <f aca="false">IF($H6="","",IFERROR(INDEX(상품목록!$C$3:$C$102,MATCH($H6,상품목록!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="14" t="str">
+        <v>35000</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="14" t="n">
         <f aca="false">IF(OR($J6="",$K6=""),"",ROUND($J6*$K6,0))</f>
-        <v/>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="14" t="str">
+        <v>105000</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14" t="n">
         <f aca="false">IF($L6="","",$L6+IF($M6="",0,$M6))</f>
-        <v/>
+        <v>105000</v>
       </c>
       <c r="O6" s="13"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="12" t="str">
         <f aca="false">IF($C6="","",IF($P6&lt;&gt;"","발송완료",IF($O6&lt;&gt;"","입금완료","입금대기")))</f>
-        <v/>
-      </c>
-      <c r="R6" s="12" t="str">
+        <v>입금대기</v>
+      </c>
+      <c r="R6" s="12" t="n">
         <f aca="false">IF($C6="","",COUNTIFS($C$3:$C6,$C6))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S6" s="12" t="str">
         <f aca="false">IF($C6="","",$C6&amp;"|"&amp;$R6)</f>
-        <v/>
+        <v>1002|2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40871,8 +40955,10 @@
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>64</v>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>260903-001</t>
+        </is>
       </c>
       <c r="C3" s="17" t="s">
         <v>65</v>
@@ -40884,7 +40970,7 @@
       </c>
       <c r="B5" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$D$3:$D$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>김고객</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -40895,7 +40981,7 @@
       </c>
       <c r="B6" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$E$3:$E$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>010-0000-0000</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -40906,7 +40992,7 @@
       </c>
       <c r="B7" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$F$3:$F$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>12345</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -40917,7 +41003,7 @@
       </c>
       <c r="B8" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$G$3:$G$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>서울시 ○○구 ○○로 10 101동 101호</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -40928,7 +41014,7 @@
       </c>
       <c r="B9" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$H$3:$H$602,MATCH($B$3,주문접수!$A$3:$A$602,0))&amp;" / "&amp;INDEX(주문접수!$I$3:$I$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>사과 부사 5kg / 5kg (특)</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -40937,9 +41023,9 @@
       <c r="A10" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="19" t="n">
         <f aca="false">IFERROR(INDEX(주문접수!$K$3:$K$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -40950,7 +41036,7 @@
       </c>
       <c r="B11" s="19" t="str">
         <f aca="false">IFERROR(INDEX(주문접수!$Q$3:$Q$602,MATCH($B$3,주문접수!$A$3:$A$602,0)),"")</f>
-        <v/>
+        <v>발송완료</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
@@ -41058,11 +41144,11 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="n">
         <f aca="false">COUNTIFS(주문접수!$C$3:$C$602,$B$3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">SUMIFS(주문접수!$N$3:$N$602,주문접수!$C$3:$C$602,$B$3)</f>
-        <v>0</v>
+        <v>132000</v>
       </c>
       <c r="E6" s="26" t="n">
         <f aca="false">COUNTIFS(주문접수!$C$3:$C$602,$B$3,주문접수!$Q$3:$Q$602,"입금대기")</f>
@@ -41096,58 +41182,58 @@
       <c r="A8" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="30" t="str">
+      <c r="B8" s="30" t="n">
         <f aca="false">IFERROR(INDEX(주문접수!$B$3:$B$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),"")</f>
-        <v/>
+        <v>46268</v>
       </c>
       <c r="C8" s="12" t="str">
         <f aca="false">IF($B8="","",IFERROR(INDEX(주문접수!$A$3:$A$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>260903-001</v>
       </c>
       <c r="D8" s="12" t="str">
         <f aca="false">IF($B8="","",IFERROR(INDEX(주문접수!$H$3:$H$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E8" s="12" t="str">
+        <v>사과 부사 5kg</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <f aca="false">IF($B8="","",IFERROR(INDEX(주문접수!$K$3:$K$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F8" s="14" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14" t="n">
         <f aca="false">IF($B8="","",IFERROR(INDEX(주문접수!$N$3:$N$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>73500</v>
       </c>
       <c r="G8" s="12" t="str">
         <f aca="false">IF($B8="","",IFERROR(INDEX(주문접수!$Q$3:$Q$602,MATCH($B$3&amp;"|"&amp;1,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>발송완료</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="30" t="str">
+      <c r="B9" s="30" t="n">
         <f aca="false">IFERROR(INDEX(주문접수!$B$3:$B$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),"")</f>
-        <v/>
+        <v>46274</v>
       </c>
       <c r="C9" s="12" t="str">
         <f aca="false">IF($B9="","",IFERROR(INDEX(주문접수!$A$3:$A$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>260909-001</v>
       </c>
       <c r="D9" s="12" t="str">
         <f aca="false">IF($B9="","",IFERROR(INDEX(주문접수!$H$3:$H$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E9" s="12" t="str">
+        <v>사과 부사 10kg</v>
+      </c>
+      <c r="E9" s="12" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(주문접수!$K$3:$K$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F9" s="14" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="n">
         <f aca="false">IF($B9="","",IFERROR(INDEX(주문접수!$N$3:$N$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>58500</v>
       </c>
       <c r="G9" s="12" t="str">
         <f aca="false">IF($B9="","",IFERROR(INDEX(주문접수!$Q$3:$Q$602,MATCH($B$3&amp;"|"&amp;2,주문접수!$S$3:$S$602,0)),""))</f>
-        <v/>
+        <v>입금완료</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42306,7 +42392,7 @@
         <v>82</v>
       </c>
       <c r="B3" s="31" t="n">
-        <v>46086</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>65</v>
@@ -42318,7 +42404,7 @@
       </c>
       <c r="B5" s="32" t="n">
         <f aca="false">COUNTIFS(주문접수!$B$3:$B$602,$B$3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42327,7 +42413,7 @@
       </c>
       <c r="B6" s="33" t="n">
         <f aca="false">SUMIFS(주문접수!$N$3:$N$602,주문접수!$B$3:$B$602,$B$3)</f>
-        <v>0</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42336,7 +42422,7 @@
       </c>
       <c r="B7" s="32" t="n">
         <f aca="false">COUNTIFS(주문접수!$O$3:$O$602,$B$3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42345,7 +42431,7 @@
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">SUMIFS(주문접수!$N$3:$N$602,주문접수!$O$3:$O$602,$B$3)</f>
-        <v>0</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42354,7 +42440,7 @@
       </c>
       <c r="B9" s="32" t="n">
         <f aca="false">COUNTIFS(주문접수!$Q$3:$Q$602,"입금대기")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42363,7 +42449,7 @@
       </c>
       <c r="B10" s="33" t="n">
         <f aca="false">SUMIFS(주문접수!$N$3:$N$602,주문접수!$Q$3:$Q$602,"입금대기")</f>
-        <v>0</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42372,7 +42458,7 @@
       </c>
       <c r="B11" s="32" t="n">
         <f aca="false">COUNTIFS(주문접수!$Q$3:$Q$602,"입금완료")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42381,7 +42467,7 @@
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">COUNTIFS(주문접수!$Q$3:$Q$602,"발송완료")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
